--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8DDFDB-E7B7-4FE4-96EB-6838374F0815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B755245-4235-42B4-9555-3C87FD69B140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="10152" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Can" sheetId="1" r:id="rId1"/>
@@ -929,10 +929,10 @@
         <v>25</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B25" s="14">
         <f>COUNTIF(Can!A9:G23, "Done")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B755245-4235-42B4-9555-3C87FD69B140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48C93CB-072D-4A88-8461-34DC934A40F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -977,7 +977,7 @@
       <c r="A14" s="23"/>
       <c r="B14" s="26"/>
       <c r="C14" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>26</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B25" s="14">
         <f>COUNTIF(Can!A9:G23, "Done")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48C93CB-072D-4A88-8461-34DC934A40F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E0A33A-13E5-45E3-BF15-4AA921254F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -980,7 +980,7 @@
         <v>25</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>26</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B25" s="14">
         <f>COUNTIF(Can!A9:G23, "Done")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E0A33A-13E5-45E3-BF15-4AA921254F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5702979D-3026-45EA-A2E3-9D5C8279358E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="47">
   <si>
     <t>Private Classes</t>
   </si>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>30.03.2026</t>
+  </si>
+  <si>
+    <t>postpone</t>
+  </si>
+  <si>
+    <t>06.04.2026</t>
   </si>
 </sst>
 </file>
@@ -983,13 +989,13 @@
         <v>25</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1034,13 +1040,13 @@
       <c r="A17" s="23"/>
       <c r="B17" s="26"/>
       <c r="C17" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>26</v>
@@ -1109,7 +1115,9 @@
     <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
       <c r="B21" s="26"/>
-      <c r="C21" s="7"/>
+      <c r="C21" s="8" t="s">
+        <v>46</v>
+      </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -1118,7 +1126,9 @@
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="23"/>
       <c r="B22" s="26"/>
-      <c r="C22" s="9"/>
+      <c r="C22" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -1127,7 +1137,9 @@
     <row r="23" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="9"/>
+      <c r="C23" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="D23" s="10"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -1148,7 +1160,7 @@
       </c>
       <c r="B25" s="14">
         <f>COUNTIF(Can!A9:G23, "Done")</f>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>
@@ -1318,7 +1330,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C11:G11 C14:G14 C17:G17 C20:G20" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C11:G11 C14:G14 C17:G17 C20:G20 C23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Done,postpone,Undone"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5702979D-3026-45EA-A2E3-9D5C8279358E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3503A4D-2896-4F94-B818-BF816F2B89D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3503A4D-2896-4F94-B818-BF816F2B89D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C9DAF1-764F-402D-9AEB-51E34B58C7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="48">
   <si>
     <t>Private Classes</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t>06.04.2026</t>
+  </si>
+  <si>
+    <t>07.04.2026</t>
   </si>
 </sst>
 </file>
@@ -1049,10 +1052,10 @@
         <v>25</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1097,10 +1100,10 @@
       <c r="A20" s="23"/>
       <c r="B20" s="26"/>
       <c r="C20" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>26</v>
@@ -1118,7 +1121,9 @@
       <c r="C21" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="8"/>
+      <c r="D21" s="8" t="s">
+        <v>47</v>
+      </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
@@ -1129,7 +1134,9 @@
       <c r="C22" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="10"/>
+      <c r="D22" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -1140,7 +1147,9 @@
       <c r="C23" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="10"/>
+      <c r="D23" s="12" t="s">
+        <v>26</v>
+      </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -1160,7 +1169,7 @@
       </c>
       <c r="B25" s="14">
         <f>COUNTIF(Can!A9:G23, "Done")</f>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>
@@ -1330,7 +1339,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C11:G11 C14:G14 C17:G17 C20:G20 C23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C11:G11 C14:G14 C17:G17 C20:G20 C23:D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Done,postpone,Undone"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69C9DAF1-764F-402D-9AEB-51E34B58C7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC33F7B-7A0A-4BF0-BA77-A25967F70C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1106,10 +1106,10 @@
         <v>25</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>26</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B25" s="14">
         <f>COUNTIF(Can!A9:G23, "Done")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>

--- a/Info.xlsx
+++ b/Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Downloads\Ilets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC33F7B-7A0A-4BF0-BA77-A25967F70C08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495983F0-FDCF-4658-8F25-889DCEA1A692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,9 +105,6 @@
     <t>Done</t>
   </si>
   <si>
-    <t>Undone</t>
-  </si>
-  <si>
     <t>16.03.2026</t>
   </si>
   <si>
@@ -169,13 +166,16 @@
   </si>
   <si>
     <t>07.04.2026</t>
+  </si>
+  <si>
+    <t>Make up</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -208,6 +208,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -366,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -437,6 +444,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -948,19 +958,19 @@
       <c r="A12" s="23"/>
       <c r="B12" s="26"/>
       <c r="C12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="G12" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -998,26 +1008,26 @@
         <v>25</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="23"/>
       <c r="B15" s="26"/>
       <c r="C15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>35</v>
-      </c>
       <c r="G15" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1055,26 +1065,26 @@
         <v>25</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="23"/>
       <c r="B18" s="26"/>
       <c r="C18" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1112,17 +1122,17 @@
         <v>25</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="23"/>
       <c r="B21" s="26"/>
       <c r="C21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="E21" s="8"/>
       <c r="F21" s="8"/>
@@ -1144,11 +1154,11 @@
     <row r="23" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>26</v>
+      <c r="C23" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>47</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
@@ -1165,11 +1175,11 @@
     </row>
     <row r="25" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="14">
         <f>COUNTIF(Can!A9:G23, "Done")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18"/>
@@ -1179,7 +1189,7 @@
     </row>
     <row r="26" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="14">
         <f>COUNTIF(Can!A9:G23, "Postponed")</f>
@@ -1193,10 +1203,10 @@
     </row>
     <row r="27" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -1339,10 +1349,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C11:G11 C14:G14 C17:G17 C20:G20 C23:D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C11:G11 C14:G14 C17:G17 C20:G20" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Done,postpone,Undone"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>